--- a/ejemplos/2_Recursos_Humanos/01_Control_de_Asistencia_EJEMPLO.xlsx
+++ b/ejemplos/2_Recursos_Humanos/01_Control_de_Asistencia_EJEMPLO.xlsx
@@ -52,7 +52,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
     </font>
     <font>
       <name val="Abadi"/>
@@ -62,7 +62,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -104,7 +104,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
@@ -127,7 +127,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
@@ -155,7 +155,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -7437,7 +7437,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001B6B73"/>
+    <tabColor rgb="000E7C8B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/ejemplos/2_Recursos_Humanos/01_Control_de_Asistencia_EJEMPLO.xlsx
+++ b/ejemplos/2_Recursos_Humanos/01_Control_de_Asistencia_EJEMPLO.xlsx
@@ -1203,7 +1203,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE</t>
+          <t>FORMATOS ADMINISTRATIVOS</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1638,7 +1638,7 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
         </is>
       </c>
       <c r="G38" s="1" t="n"/>
